--- a/docs/adjuntos/1020851871/f3.m3.pp_formato_solicitud_desvinculacion_de_beneficiarios_v4.xlsx
+++ b/docs/adjuntos/1020851871/f3.m3.pp_formato_solicitud_desvinculacion_de_beneficiarios_v4.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t xml:space="preserve">PROCESO
 PROMOCIÓN Y PREVENCIÓN
@@ -1762,45 +1762,19 @@
       <c r="W6" s="40"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="33" t="s">
-        <v>42</v>
-      </c>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
       <c r="N7" s="34"/>
       <c r="O7" s="35"/>
       <c r="P7" s="36"/>
@@ -1813,45 +1787,19 @@
       <c r="W7" s="40"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>42</v>
-      </c>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="33"/>
       <c r="N8" s="34"/>
       <c r="O8" s="35"/>
       <c r="P8" s="36"/>
@@ -1864,45 +1812,19 @@
       <c r="W8" s="40"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="33" t="s">
-        <v>42</v>
-      </c>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
       <c r="N9" s="34"/>
       <c r="O9" s="35"/>
       <c r="P9" s="36"/>
@@ -1915,45 +1837,19 @@
       <c r="W9" s="40"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" s="33" t="s">
-        <v>42</v>
-      </c>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="34"/>
       <c r="O10" s="35"/>
       <c r="P10" s="36"/>
